--- a/public/results/2026/2026 Overall Standings.xlsx
+++ b/public/results/2026/2026 Overall Standings.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mthutter/CODE/golf-league-site/public/results/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04BD954C-5F36-7C4C-AC21-1D267D026ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5C81B28-2073-0640-94F8-3810E7CD51F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1580" yWindow="1840" windowWidth="31120" windowHeight="15920" xr2:uid="{1A9894EE-562E-3246-9111-2FABF9BD81D0}"/>
+    <workbookView xWindow="45540" yWindow="3380" windowWidth="31120" windowHeight="15920" xr2:uid="{1A9894EE-562E-3246-9111-2FABF9BD81D0}"/>
   </bookViews>
   <sheets>
     <sheet name="2026 Overall" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="55">
   <si>
     <t>PLAYERS</t>
   </si>
@@ -193,6 +193,15 @@
   </si>
   <si>
     <t>Pineda</t>
+  </si>
+  <si>
+    <t>WEEK 2</t>
+  </si>
+  <si>
+    <t>Mollie</t>
+  </si>
+  <si>
+    <t>Parker</t>
   </si>
 </sst>
 </file>
@@ -276,7 +285,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="41">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -485,17 +494,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -574,17 +572,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -794,13 +781,26 @@
       <bottom style="medium">
         <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -811,194 +811,209 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="2" borderId="21" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="36" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="2" borderId="22" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="38" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1340,722 +1355,967 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E0A73BD-DC86-AB41-8C3D-0D64B5D06628}">
-  <dimension ref="A1:BG26"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8" style="3"/>
+    <col min="1" max="1" width="8.6640625" style="3" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" style="3" customWidth="1"/>
     <col min="3" max="3" width="11.33203125" style="3" customWidth="1"/>
-    <col min="4" max="10" width="8" style="3"/>
-    <col min="11" max="11" width="10.6640625" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="8" style="3"/>
+    <col min="4" max="7" width="6.33203125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="6.83203125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="6.33203125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="6.5" style="3" customWidth="1"/>
+    <col min="11" max="11" width="6.83203125" style="3" customWidth="1"/>
+    <col min="12" max="12" width="6.1640625" style="3" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" style="3" customWidth="1"/>
+    <col min="14" max="16384" width="8" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="23" t="s">
+    <row r="1" spans="1:13" s="2" customFormat="1" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="42"/>
+      <c r="C1" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="5"/>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="49" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" s="50"/>
+      <c r="H1" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="I1" s="55" t="s">
         <v>45</v>
       </c>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-      <c r="J1" s="15"/>
-      <c r="K1" s="16"/>
-    </row>
-    <row r="2" spans="1:11" s="2" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="19"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="25">
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="57"/>
+    </row>
+    <row r="2" spans="1:13" s="2" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A2" s="43"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="51">
         <v>46146</v>
       </c>
-      <c r="E2" s="26"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="6" t="s">
+      <c r="E2" s="52"/>
+      <c r="F2" s="51">
+        <v>46153</v>
+      </c>
+      <c r="G2" s="52"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="J2" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="12" t="s">
+      <c r="K2" s="62" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="L2" s="58" t="s">
         <v>6</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="M2" s="58" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="21"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="27" t="s">
+    <row r="3" spans="1:13" ht="16" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="45"/>
+      <c r="B3" s="46"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="28" t="s">
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="29"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="31"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A4" s="32" t="s">
+      <c r="F3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="H3" s="54"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="61"/>
+      <c r="K3" s="63"/>
+      <c r="L3" s="71"/>
+      <c r="M3" s="71"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="34">
+      <c r="C4" s="8">
         <v>10</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="9">
         <v>39</v>
       </c>
-      <c r="E4" s="36">
+      <c r="E4" s="10">
         <v>25</v>
       </c>
-      <c r="F4" s="37">
-        <f>D4</f>
+      <c r="F4" s="75">
+        <v>37</v>
+      </c>
+      <c r="G4" s="10">
+        <v>27</v>
+      </c>
+      <c r="H4" s="11">
+        <f>D4+F4</f>
+        <v>76</v>
+      </c>
+      <c r="I4" s="14">
+        <v>2</v>
+      </c>
+      <c r="J4" s="13">
+        <v>1</v>
+      </c>
+      <c r="K4" s="68">
+        <v>1</v>
+      </c>
+      <c r="L4" s="12">
+        <f>E4+G4+J4+K4</f>
+        <v>54</v>
+      </c>
+      <c r="M4" s="15">
+        <f>L4/I4</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="18">
+        <v>22</v>
+      </c>
+      <c r="D5" s="28">
+        <v>54</v>
+      </c>
+      <c r="E5" s="20">
+        <v>22</v>
+      </c>
+      <c r="F5" s="28">
+        <v>50</v>
+      </c>
+      <c r="G5" s="20">
+        <v>26</v>
+      </c>
+      <c r="H5" s="21">
+        <f>D5+F5</f>
+        <v>104</v>
+      </c>
+      <c r="I5" s="24">
+        <v>2</v>
+      </c>
+      <c r="J5" s="23"/>
+      <c r="K5" s="66"/>
+      <c r="L5" s="22">
+        <f>E5+G5+J5+K5</f>
+        <v>48</v>
+      </c>
+      <c r="M5" s="25">
+        <f>L5/I5</f>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="18">
+        <v>1</v>
+      </c>
+      <c r="D6" s="19">
+        <v>35</v>
+      </c>
+      <c r="E6" s="20">
+        <v>20</v>
+      </c>
+      <c r="F6" s="64">
+        <v>35</v>
+      </c>
+      <c r="G6" s="20">
+        <v>20</v>
+      </c>
+      <c r="H6" s="21">
+        <f>D6+F6</f>
+        <v>70</v>
+      </c>
+      <c r="I6" s="24">
+        <v>2</v>
+      </c>
+      <c r="J6" s="23">
+        <v>1</v>
+      </c>
+      <c r="K6" s="66">
+        <v>4</v>
+      </c>
+      <c r="L6" s="22">
+        <f>E6+G6+J6+K6</f>
+        <v>45</v>
+      </c>
+      <c r="M6" s="25">
+        <f>L6/I6</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="18">
+        <v>9</v>
+      </c>
+      <c r="D7" s="27">
+        <v>42</v>
+      </c>
+      <c r="E7" s="20">
+        <v>21</v>
+      </c>
+      <c r="F7" s="27">
+        <v>40</v>
+      </c>
+      <c r="G7" s="20">
+        <v>23</v>
+      </c>
+      <c r="H7" s="21">
+        <f>D7+F7</f>
+        <v>82</v>
+      </c>
+      <c r="I7" s="24">
+        <v>2</v>
+      </c>
+      <c r="J7" s="23"/>
+      <c r="K7" s="66">
+        <v>1</v>
+      </c>
+      <c r="L7" s="22">
+        <f>E7+G7+J7+K7</f>
+        <v>45</v>
+      </c>
+      <c r="M7" s="25">
+        <f>L7/I7</f>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="18">
+        <v>11</v>
+      </c>
+      <c r="D8" s="28">
+        <v>44</v>
+      </c>
+      <c r="E8" s="20">
+        <v>21</v>
+      </c>
+      <c r="F8" s="28">
+        <v>45</v>
+      </c>
+      <c r="G8" s="20">
+        <v>20</v>
+      </c>
+      <c r="H8" s="21">
+        <f>D8+F8</f>
+        <v>89</v>
+      </c>
+      <c r="I8" s="24">
+        <v>2</v>
+      </c>
+      <c r="J8" s="23"/>
+      <c r="K8" s="66">
+        <v>1</v>
+      </c>
+      <c r="L8" s="22">
+        <f>E8+G8+J8+K8</f>
+        <v>42</v>
+      </c>
+      <c r="M8" s="25">
+        <f>L8/I8</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="18">
+        <v>15</v>
+      </c>
+      <c r="D9" s="26">
+        <v>47</v>
+      </c>
+      <c r="E9" s="20">
+        <v>22</v>
+      </c>
+      <c r="F9" s="28">
+        <v>51</v>
+      </c>
+      <c r="G9" s="20">
+        <v>18</v>
+      </c>
+      <c r="H9" s="21">
+        <f>D9+F9</f>
+        <v>98</v>
+      </c>
+      <c r="I9" s="24">
+        <v>2</v>
+      </c>
+      <c r="J9" s="23">
+        <v>1</v>
+      </c>
+      <c r="K9" s="66"/>
+      <c r="L9" s="22">
+        <f>E9+G9+J9+K9</f>
+        <v>41</v>
+      </c>
+      <c r="M9" s="25">
+        <f>L9/I9</f>
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="18">
+        <v>6</v>
+      </c>
+      <c r="D10" s="28">
+        <v>43</v>
+      </c>
+      <c r="E10" s="20">
+        <v>17</v>
+      </c>
+      <c r="F10" s="65">
+        <v>40</v>
+      </c>
+      <c r="G10" s="20">
+        <v>20</v>
+      </c>
+      <c r="H10" s="21">
+        <f>D10+F10</f>
+        <v>83</v>
+      </c>
+      <c r="I10" s="24">
+        <v>2</v>
+      </c>
+      <c r="J10" s="23">
+        <v>1</v>
+      </c>
+      <c r="K10" s="66">
+        <v>2</v>
+      </c>
+      <c r="L10" s="22">
+        <f>E10+G10+J10+K10</f>
+        <v>40</v>
+      </c>
+      <c r="M10" s="25">
+        <f>L10/I10</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="18">
+        <v>23</v>
+      </c>
+      <c r="D11" s="28">
+        <v>57</v>
+      </c>
+      <c r="E11" s="20">
+        <v>20</v>
+      </c>
+      <c r="F11" s="28">
+        <v>58</v>
+      </c>
+      <c r="G11" s="20">
+        <v>19</v>
+      </c>
+      <c r="H11" s="21">
+        <f>D11+F11</f>
+        <v>115</v>
+      </c>
+      <c r="I11" s="24">
+        <v>2</v>
+      </c>
+      <c r="J11" s="23"/>
+      <c r="K11" s="66"/>
+      <c r="L11" s="22">
+        <f>E11+G11+J11+K11</f>
         <v>39</v>
       </c>
-      <c r="G4" s="38">
+      <c r="M11" s="25">
+        <f>L11/I11</f>
+        <v>19.5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="18">
+        <v>12</v>
+      </c>
+      <c r="D12" s="28"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="28">
+        <v>52</v>
+      </c>
+      <c r="G12" s="66">
+        <v>14</v>
+      </c>
+      <c r="H12" s="21">
+        <f>D12+F12</f>
+        <v>52</v>
+      </c>
+      <c r="I12" s="24">
         <v>1</v>
       </c>
-      <c r="H4" s="39"/>
-      <c r="I4" s="40"/>
-      <c r="J4" s="41">
-        <f>E4+H4+I4</f>
-        <v>25</v>
-      </c>
-      <c r="K4" s="42">
-        <f>J4/G4</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A5" s="43" t="s">
-        <v>34</v>
-      </c>
-      <c r="B5" s="44" t="s">
+      <c r="J12" s="23"/>
+      <c r="K12" s="66"/>
+      <c r="L12" s="22">
+        <f>E12+G12+J12+K12</f>
+        <v>14</v>
+      </c>
+      <c r="M12" s="25">
+        <f t="shared" ref="M12:M27" si="0">L12/I12</f>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="28"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="28">
         <v>35</v>
       </c>
-      <c r="C5" s="45">
+      <c r="G13" s="20"/>
+      <c r="H13" s="21">
+        <f>D13+F13</f>
+        <v>35</v>
+      </c>
+      <c r="I13" s="24">
         <v>1</v>
       </c>
-      <c r="D5" s="46">
-        <v>35</v>
-      </c>
-      <c r="E5" s="47">
+      <c r="J13" s="23"/>
+      <c r="K13" s="66">
+        <v>2</v>
+      </c>
+      <c r="L13" s="22">
+        <f>E13+G13+J13+K13</f>
+        <v>2</v>
+      </c>
+      <c r="M13" s="25">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="28">
+        <v>48</v>
+      </c>
+      <c r="E14" s="20"/>
+      <c r="F14" s="28">
+        <v>48</v>
+      </c>
+      <c r="G14" s="20"/>
+      <c r="H14" s="21">
+        <f>D14+F14</f>
+        <v>96</v>
+      </c>
+      <c r="I14" s="24">
+        <v>2</v>
+      </c>
+      <c r="J14" s="23"/>
+      <c r="K14" s="66"/>
+      <c r="L14" s="22">
+        <f>E14+G14+J14+K14</f>
+        <v>0</v>
+      </c>
+      <c r="M14" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D15" s="28">
+        <v>58</v>
+      </c>
+      <c r="E15" s="20"/>
+      <c r="F15" s="28">
+        <v>61</v>
+      </c>
+      <c r="G15" s="20"/>
+      <c r="H15" s="21">
+        <f>D15+F15</f>
+        <v>119</v>
+      </c>
+      <c r="I15" s="24">
+        <v>2</v>
+      </c>
+      <c r="J15" s="23"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="22">
+        <f>E15+G15+J15+K15</f>
+        <v>0</v>
+      </c>
+      <c r="M15" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="28">
+        <v>50</v>
+      </c>
+      <c r="E16" s="20"/>
+      <c r="F16" s="28">
+        <v>46</v>
+      </c>
+      <c r="G16" s="20"/>
+      <c r="H16" s="21">
+        <f>D16+F16</f>
+        <v>96</v>
+      </c>
+      <c r="I16" s="24">
+        <v>2</v>
+      </c>
+      <c r="J16" s="23"/>
+      <c r="K16" s="66"/>
+      <c r="L16" s="22">
+        <f>E16+G16+J16+K16</f>
+        <v>0</v>
+      </c>
+      <c r="M16" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="28">
+        <v>51</v>
+      </c>
+      <c r="E17" s="20"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="20"/>
+      <c r="H17" s="21">
+        <f>D17+F17</f>
+        <v>51</v>
+      </c>
+      <c r="I17" s="24">
+        <v>1</v>
+      </c>
+      <c r="J17" s="23"/>
+      <c r="K17" s="66"/>
+      <c r="L17" s="22">
+        <f>E17+G17+J17+K17</f>
+        <v>0</v>
+      </c>
+      <c r="M17" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="28"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="28">
+        <v>52</v>
+      </c>
+      <c r="G18" s="20"/>
+      <c r="H18" s="21">
+        <f>D18+F18</f>
+        <v>52</v>
+      </c>
+      <c r="I18" s="24">
+        <v>1</v>
+      </c>
+      <c r="J18" s="23"/>
+      <c r="K18" s="66"/>
+      <c r="L18" s="22">
+        <f>E18+G18+J18+K18</f>
+        <v>0</v>
+      </c>
+      <c r="M18" s="25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="18">
+        <v>13</v>
+      </c>
+      <c r="D19" s="28"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="20"/>
+      <c r="H19" s="21">
+        <f>D19+F19</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="24"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="66"/>
+      <c r="L19" s="22">
+        <f>E19+G19+J19+K19</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="25"/>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="18">
+        <v>18</v>
+      </c>
+      <c r="D20" s="28"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="21">
+        <f>D20+F20</f>
+        <v>0</v>
+      </c>
+      <c r="I20" s="24"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="66"/>
+      <c r="L20" s="22">
+        <f>E20+G20+J20+K20</f>
+        <v>0</v>
+      </c>
+      <c r="M20" s="25"/>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C21" s="18">
+        <v>14</v>
+      </c>
+      <c r="D21" s="28"/>
+      <c r="E21" s="20"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="21">
+        <f>D21+F21</f>
+        <v>0</v>
+      </c>
+      <c r="I21" s="24"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="66"/>
+      <c r="L21" s="22">
+        <f>E21+G21+J21+K21</f>
+        <v>0</v>
+      </c>
+      <c r="M21" s="25"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="18">
+        <v>6</v>
+      </c>
+      <c r="D22" s="28"/>
+      <c r="E22" s="20"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="20"/>
+      <c r="H22" s="21">
+        <f>D22+F22</f>
+        <v>0</v>
+      </c>
+      <c r="I22" s="24"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="66"/>
+      <c r="L22" s="22">
+        <f>E22+G22+J22+K22</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="25"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="18">
+        <v>11</v>
+      </c>
+      <c r="D23" s="28"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="21">
+        <f>D23+F23</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="24"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="69"/>
+      <c r="L23" s="22">
+        <f>E23+G23+J23+K23</f>
+        <v>0</v>
+      </c>
+      <c r="M23" s="25"/>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="C24" s="18">
+        <v>11</v>
+      </c>
+      <c r="D24" s="28"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="21">
+        <f>D24+F24</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="24"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="66"/>
+      <c r="L24" s="22">
+        <f>E24+G24+J24+K24</f>
+        <v>0</v>
+      </c>
+      <c r="M24" s="25"/>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="48">
-        <f>D5</f>
-        <v>35</v>
-      </c>
-      <c r="G5" s="49">
-        <v>1</v>
-      </c>
-      <c r="H5" s="50">
-        <v>1</v>
-      </c>
-      <c r="I5" s="51">
-        <v>2</v>
-      </c>
-      <c r="J5" s="52">
-        <f>E5+H5+I5</f>
-        <v>23</v>
-      </c>
-      <c r="K5" s="53">
-        <f>J5/G5</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="45">
+      <c r="B25" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="54">
-        <v>47</v>
-      </c>
-      <c r="E6" s="47">
-        <v>22</v>
-      </c>
-      <c r="F6" s="48">
-        <f>D6</f>
-        <v>47</v>
-      </c>
-      <c r="G6" s="49">
-        <v>1</v>
-      </c>
-      <c r="H6" s="50">
-        <v>1</v>
-      </c>
-      <c r="I6" s="51"/>
-      <c r="J6" s="52">
-        <f>E6+H6+I6</f>
-        <v>23</v>
-      </c>
-      <c r="K6" s="53">
-        <f>J6/G6</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="43" t="s">
+      <c r="C25" s="18">
         <v>18</v>
       </c>
-      <c r="B7" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="C7" s="45">
-        <v>9</v>
-      </c>
-      <c r="D7" s="55">
-        <v>42</v>
-      </c>
-      <c r="E7" s="47">
-        <v>21</v>
-      </c>
-      <c r="F7" s="48">
-        <f>D7</f>
-        <v>42</v>
-      </c>
-      <c r="G7" s="49">
-        <v>1</v>
-      </c>
-      <c r="H7" s="50"/>
-      <c r="I7" s="51">
-        <v>1</v>
-      </c>
-      <c r="J7" s="52">
-        <f>E7+H7+I7</f>
-        <v>22</v>
-      </c>
-      <c r="K7" s="53">
-        <f>J7/G7</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="43" t="s">
+      <c r="D25" s="28"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="21">
+        <f>D25+F25</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="24"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="66"/>
+      <c r="L25" s="22">
+        <f>E25+G25+J25+K25</f>
+        <v>0</v>
+      </c>
+      <c r="M25" s="25"/>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="C26" s="18">
         <v>17</v>
       </c>
-      <c r="B8" s="44" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="45">
-        <v>22</v>
-      </c>
-      <c r="D8" s="56">
-        <v>54</v>
-      </c>
-      <c r="E8" s="47">
-        <v>22</v>
-      </c>
-      <c r="F8" s="48">
-        <f>D8</f>
-        <v>54</v>
-      </c>
-      <c r="G8" s="49">
-        <v>1</v>
-      </c>
-      <c r="H8" s="50"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="52">
-        <f>E8+H8+I8</f>
-        <v>22</v>
-      </c>
-      <c r="K8" s="53">
-        <f>J8/G8</f>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="43" t="s">
+      <c r="D26" s="28"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="28"/>
+      <c r="G26" s="20"/>
+      <c r="H26" s="21">
+        <f>D26+F26</f>
+        <v>0</v>
+      </c>
+      <c r="I26" s="24"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="66"/>
+      <c r="L26" s="22">
+        <f>E26+G26+J26+K26</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="25"/>
+    </row>
+    <row r="27" spans="1:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="30" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C27" s="32">
         <v>12</v>
       </c>
-      <c r="B9" s="44" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="45">
-        <v>11</v>
-      </c>
-      <c r="D9" s="56">
-        <v>44</v>
-      </c>
-      <c r="E9" s="47">
-        <v>21</v>
-      </c>
-      <c r="F9" s="48">
-        <f>D9</f>
-        <v>44</v>
-      </c>
-      <c r="G9" s="49">
-        <v>1</v>
-      </c>
-      <c r="H9" s="50"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="52">
-        <f>E9+H9+I9</f>
-        <v>21</v>
-      </c>
-      <c r="K9" s="53">
-        <f>J9/G9</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="45">
-        <v>23</v>
-      </c>
-      <c r="D10" s="56">
-        <v>57</v>
-      </c>
-      <c r="E10" s="47">
-        <v>20</v>
-      </c>
-      <c r="F10" s="48">
-        <f>D10</f>
-        <v>57</v>
-      </c>
-      <c r="G10" s="49">
-        <v>1</v>
-      </c>
-      <c r="H10" s="50"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="52">
-        <f>E10+H10+I10</f>
-        <v>20</v>
-      </c>
-      <c r="K10" s="53">
-        <f>J10/G10</f>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="43" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="44" t="s">
-        <v>26</v>
-      </c>
-      <c r="C11" s="45">
-        <v>6</v>
-      </c>
-      <c r="D11" s="56">
-        <v>43</v>
-      </c>
-      <c r="E11" s="47">
-        <v>17</v>
-      </c>
-      <c r="F11" s="48">
-        <f>D11</f>
-        <v>43</v>
-      </c>
-      <c r="G11" s="49">
-        <v>1</v>
-      </c>
-      <c r="H11" s="50"/>
-      <c r="I11" s="51"/>
-      <c r="J11" s="52">
-        <f>E11+H11+I11</f>
-        <v>17</v>
-      </c>
-      <c r="K11" s="53">
-        <f>J11/G11</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="44" t="s">
-        <v>47</v>
-      </c>
-      <c r="C12" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="56">
-        <v>48</v>
-      </c>
-      <c r="E12" s="47"/>
-      <c r="F12" s="48">
-        <f>D12</f>
-        <v>48</v>
-      </c>
-      <c r="G12" s="49">
-        <v>1</v>
-      </c>
-      <c r="H12" s="50"/>
-      <c r="I12" s="51"/>
-      <c r="J12" s="52">
-        <f>E12+H12+I12</f>
-        <v>0</v>
-      </c>
-      <c r="K12" s="53"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="B13" s="44" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="D13" s="56">
-        <v>50</v>
-      </c>
-      <c r="E13" s="47"/>
-      <c r="F13" s="48">
-        <f>D13</f>
-        <v>50</v>
-      </c>
-      <c r="G13" s="49">
-        <v>1</v>
-      </c>
-      <c r="H13" s="50"/>
-      <c r="I13" s="51"/>
-      <c r="J13" s="52">
-        <f>E13+H13+I13</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="53"/>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="B14" s="44" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="D14" s="56">
-        <v>51</v>
-      </c>
-      <c r="E14" s="47"/>
-      <c r="F14" s="48">
-        <f>D14</f>
-        <v>51</v>
-      </c>
-      <c r="G14" s="49">
-        <v>1</v>
-      </c>
-      <c r="H14" s="50"/>
-      <c r="I14" s="51"/>
-      <c r="J14" s="52">
-        <f>E14+H14+I14</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="53"/>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="43" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="44" t="s">
-        <v>51</v>
-      </c>
-      <c r="C15" s="45" t="s">
-        <v>27</v>
-      </c>
-      <c r="D15" s="56">
-        <v>58</v>
-      </c>
-      <c r="E15" s="47"/>
-      <c r="F15" s="48">
-        <f>D15</f>
-        <v>58</v>
-      </c>
-      <c r="G15" s="49">
-        <v>1</v>
-      </c>
-      <c r="H15" s="50"/>
-      <c r="I15" s="51"/>
-      <c r="J15" s="52">
-        <f>E15+H15+I15</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="53"/>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="44" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="45">
-        <v>13</v>
-      </c>
-      <c r="D16" s="56"/>
-      <c r="E16" s="47"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="49"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="51"/>
-      <c r="J16" s="52">
-        <f>E16+H16+I16</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="53"/>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="B17" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="45">
-        <v>18</v>
-      </c>
-      <c r="D17" s="56"/>
-      <c r="E17" s="47"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="49"/>
-      <c r="H17" s="50"/>
-      <c r="I17" s="51"/>
-      <c r="J17" s="52">
-        <f>E17+H17+I17</f>
-        <v>0</v>
-      </c>
-      <c r="K17" s="53"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="B18" s="44" t="s">
-        <v>31</v>
-      </c>
-      <c r="C18" s="45">
-        <v>14</v>
-      </c>
-      <c r="D18" s="56"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="48"/>
-      <c r="G18" s="49"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="51"/>
-      <c r="J18" s="52">
-        <f>E18+H18+I18</f>
-        <v>0</v>
-      </c>
-      <c r="K18" s="53"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A19" s="43" t="s">
-        <v>12</v>
-      </c>
-      <c r="B19" s="44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" s="45">
-        <v>6</v>
-      </c>
-      <c r="D19" s="56"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="48"/>
-      <c r="G19" s="49"/>
-      <c r="H19" s="50"/>
-      <c r="I19" s="51"/>
-      <c r="J19" s="52">
-        <f>E19+H19+I19</f>
-        <v>0</v>
-      </c>
-      <c r="K19" s="53"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="43" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="44" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="45">
-        <v>11</v>
-      </c>
-      <c r="D20" s="56"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="48"/>
-      <c r="G20" s="49"/>
-      <c r="H20" s="57"/>
-      <c r="I20" s="58"/>
-      <c r="J20" s="52">
-        <f>E20+H20+I20</f>
-        <v>0</v>
-      </c>
-      <c r="K20" s="53"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="43" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" s="44" t="s">
-        <v>37</v>
-      </c>
-      <c r="C21" s="45">
-        <v>11</v>
-      </c>
-      <c r="D21" s="56"/>
-      <c r="E21" s="47"/>
-      <c r="F21" s="48"/>
-      <c r="G21" s="49"/>
-      <c r="H21" s="50"/>
-      <c r="I21" s="51"/>
-      <c r="J21" s="52">
-        <f>E21+H21+I21</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="53"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="43" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="45">
-        <v>18</v>
-      </c>
-      <c r="D22" s="56"/>
-      <c r="E22" s="47"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="49"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="51"/>
-      <c r="J22" s="52">
-        <f>E22+H22+I22</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="53"/>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A23" s="43" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="45">
-        <v>17</v>
-      </c>
-      <c r="D23" s="56"/>
-      <c r="E23" s="47"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="49"/>
-      <c r="H23" s="50"/>
-      <c r="I23" s="51"/>
-      <c r="J23" s="52">
-        <f>E23+H23+I23</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="53"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="43" t="s">
-        <v>30</v>
-      </c>
-      <c r="B24" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="C24" s="45">
-        <v>12</v>
-      </c>
-      <c r="D24" s="56"/>
-      <c r="E24" s="47"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="49"/>
-      <c r="H24" s="50"/>
-      <c r="I24" s="51"/>
-      <c r="J24" s="52">
-        <f>E24+H24+I24</f>
-        <v>0</v>
-      </c>
-      <c r="K24" s="53"/>
-    </row>
-    <row r="25" spans="1:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="59" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="60" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="61">
-        <v>12</v>
-      </c>
-      <c r="D25" s="62"/>
-      <c r="E25" s="63"/>
-      <c r="F25" s="64"/>
-      <c r="G25" s="65"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="63"/>
-      <c r="J25" s="64">
-        <f>E25+H25+I25</f>
-        <v>0</v>
-      </c>
-      <c r="K25" s="67"/>
-    </row>
-    <row r="26" spans="1:11" s="1" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="68"/>
-      <c r="B26" s="69"/>
-      <c r="C26" s="69"/>
-      <c r="D26" s="70">
-        <f>AVERAGEIF(D4:D25,"&gt;0")</f>
+      <c r="D27" s="33"/>
+      <c r="E27" s="67"/>
+      <c r="F27" s="33"/>
+      <c r="G27" s="73"/>
+      <c r="H27" s="72">
+        <f>D27+F27</f>
+        <v>0</v>
+      </c>
+      <c r="I27" s="34"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="35">
+        <f>E27+G27+J27+K27</f>
+        <v>0</v>
+      </c>
+      <c r="M27" s="37"/>
+    </row>
+    <row r="28" spans="1:13" s="1" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="38"/>
+      <c r="B28" s="39"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="40">
+        <f>AVERAGEIF(D4:D27,"&gt;0")</f>
         <v>47.333333333333336</v>
       </c>
-      <c r="E26" s="70"/>
-      <c r="F26" s="67"/>
+      <c r="E28" s="40"/>
+      <c r="F28" s="40">
+        <f>AVERAGEIF(F4:F27,"&gt;0")</f>
+        <v>46.428571428571431</v>
+      </c>
+      <c r="G28" s="40"/>
+      <c r="H28" s="74"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:M27">
+    <sortCondition descending="1" ref="M4:M27"/>
+    <sortCondition descending="1" ref="L4:L27"/>
+    <sortCondition descending="1" ref="I4:I27"/>
+    <sortCondition ref="B4:B27"/>
+  </sortState>
+  <mergeCells count="13">
+    <mergeCell ref="I1:M1"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
     <mergeCell ref="A1:B3"/>
     <mergeCell ref="C1:C3"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F1:F3"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="H2:H3"/>
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="H1:H3"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="F2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
